--- a/artfynd/A 29840-2023 artfynd.xlsx
+++ b/artfynd/A 29840-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129523796</v>
       </c>
       <c r="B2" t="n">
-        <v>58097</v>
+        <v>58100</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29840-2023 artfynd.xlsx
+++ b/artfynd/A 29840-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129523796</v>
       </c>
       <c r="B2" t="n">
-        <v>58100</v>
+        <v>58105</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29840-2023 artfynd.xlsx
+++ b/artfynd/A 29840-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129523796</v>
       </c>
       <c r="B2" t="n">
-        <v>58105</v>
+        <v>58106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29840-2023 artfynd.xlsx
+++ b/artfynd/A 29840-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129523796</v>
+        <v>129523777</v>
       </c>
       <c r="B2" t="n">
-        <v>58106</v>
+        <v>58497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>606458</v>
+        <v>606538</v>
       </c>
       <c r="R2" t="n">
-        <v>6726944</v>
+        <v>6726925</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,14 +770,498 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Bergslagsbanan fågelinventeringar C240036</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129523796</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bergslagsbanan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>606458</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6726944</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Elin Lönnberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
           <t>Petter Andersson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Bergslagsbanan fågelinventeringar C240036</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121626075</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56823</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bergslagenbanan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>606377</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6726855</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>André Dabolins</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jacqueline Nelms, David Alvunger</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121626087</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bergslagenbanan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>606377</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6726855</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>André Dabolins</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jacqueline Nelms, David Alvunger</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121626058</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bergslagenbanan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>606377</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6726855</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>André Dabolins</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jacqueline Nelms, David Alvunger</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29840-2023 artfynd.xlsx
+++ b/artfynd/A 29840-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Bergslagsbanan fågelinventeringar C240036</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129523777</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Bergslagsbanan fågelinventeringar C240036</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129523796</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121626075</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121626087</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1262,8 +1287,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121626058</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>